--- a/jogos_2025-06-12.xlsx
+++ b/jogos_2025-06-12.xlsx
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,77 +1056,77 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>3.9</v>
       </c>
       <c r="M5" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>11.1</v>
+        <v>1.91</v>
       </c>
       <c r="O5" t="n">
-        <v>1.84</v>
+        <v>4.65</v>
       </c>
       <c r="P5" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.1</v>
+        <v>2.51</v>
       </c>
       <c r="R5" t="n">
         <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="T5" t="n">
-        <v>3.01</v>
+        <v>3.46</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['64', '52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '86']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.3</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,77 +1314,77 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.91</v>
+        <v>11.1</v>
       </c>
       <c r="O7" t="n">
-        <v>4.65</v>
+        <v>1.84</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.51</v>
+        <v>11.1</v>
       </c>
       <c r="R7" t="n">
         <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>3.46</v>
+        <v>3.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>['64', '52']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['21', '86']</t>
-        </is>
-      </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>3.3</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.89</v>
+        <v>3.52</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="O8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.35</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>2.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="X8" t="n">
-        <v>6.4</v>
+        <v>2.44</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>2.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>5.16</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.3</v>
+        <v>1.93</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.28</v>
+        <v>1.75</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45820.79166666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.52</v>
+        <v>1.89</v>
       </c>
       <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.33</v>
-      </c>
       <c r="O10" t="n">
-        <v>4.75</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC10" t="n">
-        <v>1.93</v>
+        <v>1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>3.28</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45820.79166666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
-        <v>4.15</v>
+        <v>3.03</v>
       </c>
       <c r="N12" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>2.3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['11', '43']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.05</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45820.83333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>4.15</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>3.47</v>
       </c>
       <c r="O13" t="n">
-        <v>3.08</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>3.58</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="V13" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.42</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>1.97</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.15</v>
+        <v>1.39</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['11', '43']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45820.83333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>5.31</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.39</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="P15" t="n">
         <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X15" t="n">
-        <v>4.8</v>
+        <v>3.72</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['17', '46', '77', '74']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['53', '59']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45820.875</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.31</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>1.59</v>
+        <v>3.39</v>
       </c>
       <c r="O16" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
         <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['17', '46', '77', '74']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.2</v>
       </c>
-      <c r="X16" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AH16" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['53', '59']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI16" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45820.875</v>
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="O17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.5</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.6</v>
-      </c>
       <c r="Y17" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['30', '90+4']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40', '26', '69']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AI17" t="n">
         <v>1.57</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45820.89583333334</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="M18" t="n">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>5.05</v>
       </c>
       <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.55</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['30', '90+4']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['40', '26', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AI18" t="n">
         <v>1.57</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45820.89583333334</v>
